--- a/prototype/signature-template.xlsx
+++ b/prototype/signature-template.xlsx
@@ -44,7 +44,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0."/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -64,6 +64,12 @@
     </font>
     <font>
       <b/>
+      <u/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
       <u/>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -146,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -175,7 +181,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -187,6 +193,9 @@
     <xf borderId="4" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
@@ -195,15 +204,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -537,7 +559,7 @@
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="17"/>
-      <c r="B13" s="10"/>
+      <c r="B13" s="18"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
@@ -545,7 +567,7 @@
       <c r="G13" s="10"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
-      <c r="A14" s="18"/>
+      <c r="A14" s="19"/>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
@@ -554,8 +576,8 @@
       <c r="G14" s="13"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="A15" s="18"/>
-      <c r="B15" s="19"/>
+      <c r="A15" s="19"/>
+      <c r="B15" s="20"/>
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -563,8 +585,8 @@
       <c r="G15" s="13"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
+      <c r="A16" s="19"/>
+      <c r="B16" s="20"/>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -572,8 +594,8 @@
       <c r="G16" s="13"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
+      <c r="A17" s="19"/>
+      <c r="B17" s="20"/>
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
@@ -581,8 +603,8 @@
       <c r="G17" s="13"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
-      <c r="A18" s="20"/>
-      <c r="B18" s="21"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
       <c r="E18" s="16"/>
@@ -591,7 +613,7 @@
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="17"/>
-      <c r="B19" s="22"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="10"/>
       <c r="D19" s="11"/>
       <c r="E19" s="11"/>
@@ -599,7 +621,7 @@
       <c r="G19" s="11"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
-      <c r="A20" s="18"/>
+      <c r="A20" s="19"/>
       <c r="B20" s="13"/>
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
@@ -608,8 +630,8 @@
       <c r="G20" s="13"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="A21" s="18"/>
-      <c r="B21" s="19"/>
+      <c r="A21" s="19"/>
+      <c r="B21" s="20"/>
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -617,8 +639,8 @@
       <c r="G21" s="13"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="A22" s="18"/>
-      <c r="B22" s="19"/>
+      <c r="A22" s="19"/>
+      <c r="B22" s="20"/>
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -626,8 +648,8 @@
       <c r="G22" s="13"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
-      <c r="A23" s="18"/>
-      <c r="B23" s="19"/>
+      <c r="A23" s="19"/>
+      <c r="B23" s="20"/>
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
@@ -635,8 +657,8 @@
       <c r="G23" s="13"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="A24" s="20"/>
-      <c r="B24" s="21"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
       <c r="E24" s="16"/>
@@ -645,7 +667,7 @@
     </row>
     <row r="25" ht="14.25" customHeight="1">
       <c r="A25" s="17"/>
-      <c r="B25" s="22"/>
+      <c r="B25" s="18"/>
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="10"/>
@@ -653,7 +675,7 @@
       <c r="G25" s="10"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="18"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="13"/>
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
@@ -662,8 +684,8 @@
       <c r="G26" s="13"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="18"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="19"/>
+      <c r="B27" s="20"/>
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
@@ -671,8 +693,8 @@
       <c r="G27" s="13"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="18"/>
-      <c r="B28" s="19"/>
+      <c r="A28" s="19"/>
+      <c r="B28" s="20"/>
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -680,8 +702,8 @@
       <c r="G28" s="13"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="18"/>
-      <c r="B29" s="19"/>
+      <c r="A29" s="19"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -690,19 +712,67 @@
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="23"/>
-      <c r="B30" s="21"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
       <c r="F30" s="16"/>
       <c r="G30" s="16"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1">
+      <c r="A31" s="17"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
+    </row>
+    <row r="32" ht="14.25" customHeight="1">
+      <c r="A32" s="19"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" ht="14.25" customHeight="1">
+      <c r="A33" s="19"/>
+      <c r="B33" s="20"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+    </row>
+    <row r="34" ht="14.25" customHeight="1">
+      <c r="A34" s="19"/>
+      <c r="B34" s="20"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="19"/>
+      <c r="B35" s="20"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+    </row>
+    <row r="36" ht="14.25" customHeight="1">
+      <c r="A36" s="23"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="16"/>
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+    </row>
     <row r="37" ht="14.25" customHeight="1"/>
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
@@ -1674,6 +1744,11 @@
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A4:G4"/>
   </mergeCells>
+  <conditionalFormatting sqref="B31">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(B31))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <printOptions/>
   <pageMargins bottom="0.984251968503937" footer="0.0" header="0.0" left="0.8267716535433072" right="0.35433070866141736" top="0.984251968503937"/>
   <pageSetup paperSize="9" orientation="portrait"/>
